--- a/finance/data/TO Score.xlsx
+++ b/finance/data/TO Score.xlsx
@@ -2207,7 +2207,9 @@
       <c r="F2" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G2" s="25" t="n"/>
+      <c r="G2" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H2" s="25" t="n"/>
       <c r="I2" s="25" t="n"/>
       <c r="J2" s="25" t="n"/>
@@ -2296,7 +2298,9 @@
       <c r="G4" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H4" s="25" t="n"/>
+      <c r="H4" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I4" s="25" t="n"/>
       <c r="J4" s="25" t="n"/>
       <c r="K4" s="25" t="n"/>
@@ -2428,7 +2432,9 @@
       <c r="G7" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H7" s="25" t="n"/>
+      <c r="H7" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I7" s="25" t="n"/>
       <c r="J7" s="25" t="n"/>
       <c r="K7" s="25" t="n"/>
@@ -2472,7 +2478,9 @@
       <c r="G8" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H8" s="25" t="n"/>
+      <c r="H8" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I8" s="25" t="n"/>
       <c r="J8" s="25" t="n"/>
       <c r="K8" s="25" t="n"/>
@@ -2729,7 +2737,9 @@
       <c r="F14" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G14" s="25" t="n"/>
+      <c r="G14" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H14" s="25" t="n"/>
       <c r="I14" s="25" t="n"/>
       <c r="J14" s="25" t="n"/>
@@ -2777,18 +2787,10 @@
       <c r="H15" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="I15" s="25" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L15" s="25" t="n">
-        <v>20000</v>
-      </c>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="25" t="n"/>
       <c r="M15" s="25" t="n"/>
       <c r="N15" s="25" t="n"/>
       <c r="O15" s="25" t="n"/>
@@ -2828,7 +2830,9 @@
       <c r="G16" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H16" s="25" t="n"/>
+      <c r="H16" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I16" s="25" t="n"/>
       <c r="J16" s="25" t="n"/>
       <c r="K16" s="25" t="n"/>
@@ -2869,7 +2873,9 @@
       <c r="F17" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G17" s="25" t="n"/>
+      <c r="G17" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H17" s="25" t="n"/>
       <c r="I17" s="25" t="n"/>
       <c r="J17" s="25" t="n"/>
@@ -2911,8 +2917,12 @@
       <c r="F18" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G18" s="25" t="n"/>
-      <c r="H18" s="25" t="n"/>
+      <c r="G18" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I18" s="25" t="n"/>
       <c r="J18" s="25" t="n"/>
       <c r="K18" s="25" t="n"/>
@@ -2953,7 +2963,9 @@
       <c r="F19" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G19" s="25" t="n"/>
+      <c r="G19" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H19" s="25" t="n"/>
       <c r="I19" s="25" t="n"/>
       <c r="J19" s="25" t="n"/>
@@ -2995,8 +3007,12 @@
       <c r="F20" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G20" s="25" t="n"/>
-      <c r="H20" s="25" t="n"/>
+      <c r="G20" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I20" s="25" t="n"/>
       <c r="J20" s="25" t="n"/>
       <c r="K20" s="25" t="n"/>
@@ -3163,7 +3179,9 @@
       <c r="F24" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G24" s="103" t="n"/>
+      <c r="G24" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H24" s="103" t="n"/>
       <c r="I24" s="103" t="n"/>
       <c r="J24" s="25" t="n"/>
@@ -3291,7 +3309,9 @@
       <c r="F27" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G27" s="103" t="n"/>
+      <c r="G27" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H27" s="103" t="n"/>
       <c r="I27" s="103" t="n"/>
       <c r="J27" s="25" t="n"/>
@@ -3376,7 +3396,9 @@
       <c r="G29" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H29" s="103" t="n"/>
+      <c r="H29" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I29" s="103" t="n"/>
       <c r="J29" s="25" t="n"/>
       <c r="K29" s="25" t="n"/>
@@ -3420,7 +3442,9 @@
       <c r="G30" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H30" s="103" t="n"/>
+      <c r="H30" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I30" s="103" t="n"/>
       <c r="J30" s="25" t="n"/>
       <c r="K30" s="25" t="n"/>
@@ -3461,7 +3485,9 @@
       <c r="F31" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G31" s="103" t="n"/>
+      <c r="G31" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H31" s="103" t="n"/>
       <c r="I31" s="103" t="n"/>
       <c r="J31" s="25" t="n"/>
@@ -3503,7 +3529,9 @@
       <c r="F32" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G32" s="103" t="n"/>
+      <c r="G32" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H32" s="103" t="n"/>
       <c r="I32" s="103" t="n"/>
       <c r="J32" s="25" t="n"/>
@@ -3586,7 +3614,9 @@
       <c r="G34" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H34" s="103" t="n"/>
+      <c r="H34" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I34" s="103" t="n"/>
       <c r="J34" s="25" t="n"/>
       <c r="K34" s="25" t="n"/>
@@ -3667,8 +3697,12 @@
       <c r="F36" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G36" s="103" t="n"/>
-      <c r="H36" s="103" t="n"/>
+      <c r="G36" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H36" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I36" s="103" t="n"/>
       <c r="J36" s="25" t="n"/>
       <c r="K36" s="25" t="n"/>
@@ -3712,7 +3746,9 @@
       <c r="G37" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H37" s="103" t="n"/>
+      <c r="H37" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I37" s="103" t="n"/>
       <c r="J37" s="25" t="n"/>
       <c r="K37" s="25" t="n"/>
@@ -3807,7 +3843,9 @@
       <c r="G39" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H39" s="103" t="n"/>
+      <c r="H39" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I39" s="103" t="n"/>
       <c r="J39" s="103" t="n"/>
       <c r="K39" s="103" t="n"/>
@@ -3851,7 +3889,9 @@
       <c r="G40" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H40" s="103" t="n"/>
+      <c r="H40" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I40" s="103" t="n"/>
       <c r="J40" s="25" t="n"/>
       <c r="K40" s="25" t="n"/>
@@ -3892,7 +3932,9 @@
       <c r="F41" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G41" s="103" t="n"/>
+      <c r="G41" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H41" s="103" t="n"/>
       <c r="I41" s="103" t="n"/>
       <c r="J41" s="25" t="n"/>
@@ -3937,7 +3979,9 @@
       <c r="G42" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H42" s="103" t="n"/>
+      <c r="H42" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I42" s="103" t="n"/>
       <c r="J42" s="25" t="n"/>
       <c r="K42" s="25" t="n"/>
@@ -3979,7 +4023,9 @@
       <c r="G43" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H43" s="103" t="n"/>
+      <c r="H43" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I43" s="103" t="n"/>
       <c r="J43" s="25" t="n"/>
       <c r="K43" s="25" t="n"/>
@@ -4019,7 +4065,9 @@
       <c r="G44" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H44" s="103" t="n"/>
+      <c r="H44" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I44" s="103" t="n"/>
       <c r="J44" s="25" t="n"/>
       <c r="K44" s="25" t="n"/>
@@ -4582,7 +4630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="13.25" customWidth="1" style="97" min="1" max="1"/>
@@ -5344,6 +5392,53 @@
           <t>월간회비납부</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4">
+        <f>RIGHT(YEAR(C21),2)&amp;"년 "&amp;MONTH(C21)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B21" s="4">
+        <f>VLOOKUP(WEEKDAY(C21,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C21" s="136" t="n">
+        <v>46263</v>
+      </c>
+      <c r="D21" s="136" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="E21" s="136" t="inlineStr">
+        <is>
+          <t>이자</t>
+        </is>
+      </c>
+      <c r="F21" s="137" t="n"/>
+      <c r="G21" s="137" t="n">
+        <v>115</v>
+      </c>
+      <c r="H21" s="138">
+        <f>G21-F21</f>
+        <v/>
+      </c>
+      <c r="I21" s="139" t="inlineStr">
+        <is>
+          <t>예금이자(8월)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="136" t="n"/>
+      <c r="D22" s="136" t="n"/>
+      <c r="E22" s="136" t="n"/>
+      <c r="F22" s="137" t="n"/>
+      <c r="G22" s="137" t="n"/>
+      <c r="H22" s="138" t="n"/>
+      <c r="I22" s="139" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/finance/data/TO Score.xlsx
+++ b/finance/data/TO Score.xlsx
@@ -2060,7 +2060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W45"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9.375" bestFit="1" customWidth="1" style="97" min="2" max="2"/>
@@ -2210,7 +2210,9 @@
       <c r="G2" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H2" s="25" t="n"/>
+      <c r="H2" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I2" s="25" t="n"/>
       <c r="J2" s="25" t="n"/>
       <c r="K2" s="25" t="n"/>
@@ -2254,7 +2256,9 @@
       <c r="G3" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H3" s="25" t="n"/>
+      <c r="H3" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I3" s="25" t="n"/>
       <c r="J3" s="25" t="n"/>
       <c r="K3" s="25" t="n"/>
@@ -2301,7 +2305,9 @@
       <c r="H4" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="I4" s="25" t="n"/>
+      <c r="I4" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="J4" s="25" t="n"/>
       <c r="K4" s="25" t="n"/>
       <c r="L4" s="25" t="n"/>
@@ -2344,7 +2350,9 @@
       <c r="G5" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H5" s="25" t="n"/>
+      <c r="H5" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I5" s="25" t="n"/>
       <c r="J5" s="25" t="n"/>
       <c r="K5" s="25" t="n"/>
@@ -2388,7 +2396,9 @@
       <c r="G6" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H6" s="25" t="n"/>
+      <c r="H6" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I6" s="25" t="n"/>
       <c r="J6" s="25" t="n"/>
       <c r="K6" s="25" t="n"/>
@@ -2435,7 +2445,9 @@
       <c r="H7" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="I7" s="25" t="n"/>
+      <c r="I7" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="J7" s="25" t="n"/>
       <c r="K7" s="25" t="n"/>
       <c r="L7" s="25" t="n"/>
@@ -2481,7 +2493,9 @@
       <c r="H8" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="I8" s="25" t="n"/>
+      <c r="I8" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="J8" s="25" t="n"/>
       <c r="K8" s="25" t="n"/>
       <c r="L8" s="25" t="n"/>
@@ -2505,7 +2519,7 @@
       </c>
       <c r="B9" s="101" t="inlineStr">
         <is>
-          <t>탈퇴</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="C9" s="102">
@@ -2564,7 +2578,9 @@
       <c r="G10" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H10" s="25" t="n"/>
+      <c r="H10" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I10" s="25" t="n"/>
       <c r="J10" s="25" t="n"/>
       <c r="K10" s="25" t="n"/>
@@ -2603,14 +2619,20 @@
         <v>20000</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="G11" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
-      <c r="J11" s="25" t="n"/>
+      <c r="H11" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J11" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="K11" s="25" t="n"/>
       <c r="L11" s="25" t="n"/>
       <c r="M11" s="25" t="n"/>
@@ -2650,12 +2672,20 @@
         <v>20000</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>40000</v>
-      </c>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="25" t="n"/>
+        <v>20000</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J12" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K12" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="L12" s="25" t="n"/>
       <c r="M12" s="25" t="n"/>
       <c r="N12" s="25" t="n"/>
@@ -2696,8 +2726,12 @@
       <c r="G13" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
+      <c r="H13" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="J13" s="25" t="n"/>
       <c r="K13" s="25" t="n"/>
       <c r="L13" s="25" t="n"/>
@@ -2740,7 +2774,9 @@
       <c r="G14" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H14" s="25" t="n"/>
+      <c r="H14" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="I14" s="25" t="n"/>
       <c r="J14" s="25" t="n"/>
       <c r="K14" s="25" t="n"/>
@@ -2787,7 +2823,9 @@
       <c r="H15" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="I15" s="25" t="n"/>
+      <c r="I15" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="J15" s="25" t="n"/>
       <c r="K15" s="25" t="n"/>
       <c r="L15" s="25" t="n"/>
@@ -2833,7 +2871,9 @@
       <c r="H16" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="I16" s="25" t="n"/>
+      <c r="I16" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="J16" s="25" t="n"/>
       <c r="K16" s="25" t="n"/>
       <c r="L16" s="25" t="n"/>
@@ -2966,8 +3006,12 @@
       <c r="G19" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
+      <c r="H19" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I19" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="J19" s="25" t="n"/>
       <c r="K19" s="25" t="n"/>
       <c r="L19" s="25" t="n"/>
@@ -3138,10 +3182,18 @@
       <c r="G23" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H23" s="103" t="n"/>
-      <c r="I23" s="103" t="n"/>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="25" t="n"/>
+      <c r="H23" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I23" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J23" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K23" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="L23" s="25" t="n"/>
       <c r="M23" s="25" t="n"/>
       <c r="N23" s="25" t="n"/>
@@ -3182,7 +3234,9 @@
       <c r="G24" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H24" s="103" t="n"/>
+      <c r="H24" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I24" s="103" t="n"/>
       <c r="J24" s="25" t="n"/>
       <c r="K24" s="25" t="n"/>
@@ -3226,7 +3280,9 @@
       <c r="G25" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H25" s="103" t="n"/>
+      <c r="H25" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I25" s="103" t="n"/>
       <c r="J25" s="25" t="n"/>
       <c r="K25" s="25" t="n"/>
@@ -3267,9 +3323,15 @@
       <c r="F26" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G26" s="103" t="n"/>
-      <c r="H26" s="103" t="n"/>
-      <c r="I26" s="103" t="n"/>
+      <c r="G26" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H26" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I26" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J26" s="25" t="n"/>
       <c r="K26" s="25" t="n"/>
       <c r="L26" s="25" t="n"/>
@@ -3312,7 +3374,9 @@
       <c r="G27" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H27" s="103" t="n"/>
+      <c r="H27" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I27" s="103" t="n"/>
       <c r="J27" s="25" t="n"/>
       <c r="K27" s="25" t="n"/>
@@ -3399,7 +3463,9 @@
       <c r="H29" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="I29" s="103" t="n"/>
+      <c r="I29" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J29" s="25" t="n"/>
       <c r="K29" s="25" t="n"/>
       <c r="L29" s="25" t="n"/>
@@ -3445,7 +3511,9 @@
       <c r="H30" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="I30" s="103" t="n"/>
+      <c r="I30" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J30" s="25" t="n"/>
       <c r="K30" s="25" t="n"/>
       <c r="L30" s="25" t="n"/>
@@ -3488,8 +3556,12 @@
       <c r="G31" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H31" s="103" t="n"/>
-      <c r="I31" s="103" t="n"/>
+      <c r="H31" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I31" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J31" s="25" t="n"/>
       <c r="K31" s="25" t="n"/>
       <c r="L31" s="25" t="n"/>
@@ -3617,7 +3689,9 @@
       <c r="H34" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="I34" s="103" t="n"/>
+      <c r="I34" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J34" s="25" t="n"/>
       <c r="K34" s="25" t="n"/>
       <c r="L34" s="25" t="n"/>
@@ -3749,7 +3823,9 @@
       <c r="H37" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="I37" s="103" t="n"/>
+      <c r="I37" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J37" s="25" t="n"/>
       <c r="K37" s="25" t="n"/>
       <c r="L37" s="25" t="n"/>
@@ -3846,7 +3922,9 @@
       <c r="H39" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="I39" s="103" t="n"/>
+      <c r="I39" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J39" s="103" t="n"/>
       <c r="K39" s="103" t="n"/>
       <c r="L39" s="103" t="n"/>
@@ -3935,7 +4013,9 @@
       <c r="G41" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="H41" s="103" t="n"/>
+      <c r="H41" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="I41" s="103" t="n"/>
       <c r="J41" s="25" t="n"/>
       <c r="K41" s="25" t="n"/>
@@ -3982,7 +4062,9 @@
       <c r="H42" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="I42" s="103" t="n"/>
+      <c r="I42" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J42" s="25" t="n"/>
       <c r="K42" s="25" t="n"/>
       <c r="L42" s="25" t="n"/>
@@ -4026,7 +4108,9 @@
       <c r="H43" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="I43" s="103" t="n"/>
+      <c r="I43" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J43" s="25" t="n"/>
       <c r="K43" s="25" t="n"/>
       <c r="L43" s="25" t="n"/>
@@ -4068,7 +4152,9 @@
       <c r="H44" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="I44" s="103" t="n"/>
+      <c r="I44" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="J44" s="25" t="n"/>
       <c r="K44" s="25" t="n"/>
       <c r="L44" s="25" t="n"/>
@@ -4084,95 +4170,133 @@
       <c r="V44" s="25" t="n"/>
       <c r="W44" s="25" t="n"/>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+    <row r="45" ht="34.5" customHeight="1" s="97">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>박승훈</t>
+        </is>
+      </c>
+      <c r="B45" s="101" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="C45" s="102">
+        <f>SUM(D45:CD45)</f>
+        <v/>
+      </c>
+      <c r="D45" s="98" t="n"/>
+      <c r="E45" s="103" t="n"/>
+      <c r="F45" s="103" t="n"/>
+      <c r="G45" s="103" t="n"/>
+      <c r="H45" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I45" s="103" t="n"/>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="25" t="n"/>
+      <c r="L45" s="25" t="n"/>
+      <c r="M45" s="25" t="n"/>
+      <c r="N45" s="25" t="n"/>
+      <c r="O45" s="25" t="n"/>
+      <c r="P45" s="25" t="n"/>
+      <c r="Q45" s="25" t="n"/>
+      <c r="R45" s="25" t="n"/>
+      <c r="S45" s="25" t="n"/>
+      <c r="T45" s="25" t="n"/>
+      <c r="U45" s="25" t="n"/>
+      <c r="V45" s="25" t="n"/>
+      <c r="W45" s="25" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>계</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n"/>
-      <c r="C45" s="102">
-        <f>SUM(C2:C44)</f>
-        <v/>
-      </c>
-      <c r="D45" s="102">
-        <f>SUM(D2:D44)</f>
-        <v/>
-      </c>
-      <c r="E45" s="102">
-        <f>SUM(E2:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="102">
-        <f>SUM(F2:F44)</f>
-        <v/>
-      </c>
-      <c r="G45" s="102">
-        <f>SUM(G2:G44)</f>
-        <v/>
-      </c>
-      <c r="H45" s="102">
-        <f>SUM(H2:H44)</f>
-        <v/>
-      </c>
-      <c r="I45" s="102">
-        <f>SUM(I2:I44)</f>
-        <v/>
-      </c>
-      <c r="J45" s="102">
-        <f>SUM(J2:J44)</f>
-        <v/>
-      </c>
-      <c r="K45" s="102">
-        <f>SUM(K2:K44)</f>
-        <v/>
-      </c>
-      <c r="L45" s="102">
-        <f>SUM(L2:L44)</f>
-        <v/>
-      </c>
-      <c r="M45" s="102">
-        <f>SUM(M2:M44)</f>
-        <v/>
-      </c>
-      <c r="N45" s="102">
-        <f>SUM(N2:N44)</f>
-        <v/>
-      </c>
-      <c r="O45" s="102">
-        <f>SUM(O2:O44)</f>
-        <v/>
-      </c>
-      <c r="P45" s="102">
-        <f>SUM(P2:P44)</f>
-        <v/>
-      </c>
-      <c r="Q45" s="102">
-        <f>SUM(Q2:Q44)</f>
-        <v/>
-      </c>
-      <c r="R45" s="102">
-        <f>SUM(R2:R44)</f>
-        <v/>
-      </c>
-      <c r="S45" s="102">
-        <f>SUM(S2:S44)</f>
-        <v/>
-      </c>
-      <c r="T45" s="102">
-        <f>SUM(T2:T44)</f>
-        <v/>
-      </c>
-      <c r="U45" s="102">
-        <f>SUM(U2:U44)</f>
-        <v/>
-      </c>
-      <c r="V45" s="102">
-        <f>SUM(V2:V44)</f>
-        <v/>
-      </c>
-      <c r="W45" s="102">
-        <f>SUM(W2:W44)</f>
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="102">
+        <f>SUM(C2:C45)</f>
+        <v/>
+      </c>
+      <c r="D46" s="102">
+        <f>SUM(D2:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="102">
+        <f>SUM(E2:E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="102">
+        <f>SUM(F2:F45)</f>
+        <v/>
+      </c>
+      <c r="G46" s="102">
+        <f>SUM(G2:G45)</f>
+        <v/>
+      </c>
+      <c r="H46" s="102">
+        <f>SUM(H2:H45)</f>
+        <v/>
+      </c>
+      <c r="I46" s="102">
+        <f>SUM(I2:I45)</f>
+        <v/>
+      </c>
+      <c r="J46" s="102">
+        <f>SUM(J2:J45)</f>
+        <v/>
+      </c>
+      <c r="K46" s="102">
+        <f>SUM(K2:K45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="102">
+        <f>SUM(L2:L45)</f>
+        <v/>
+      </c>
+      <c r="M46" s="102">
+        <f>SUM(M2:M45)</f>
+        <v/>
+      </c>
+      <c r="N46" s="102">
+        <f>SUM(N2:N45)</f>
+        <v/>
+      </c>
+      <c r="O46" s="102">
+        <f>SUM(O2:O45)</f>
+        <v/>
+      </c>
+      <c r="P46" s="102">
+        <f>SUM(P2:P45)</f>
+        <v/>
+      </c>
+      <c r="Q46" s="102">
+        <f>SUM(Q2:Q45)</f>
+        <v/>
+      </c>
+      <c r="R46" s="102">
+        <f>SUM(R2:R45)</f>
+        <v/>
+      </c>
+      <c r="S46" s="102">
+        <f>SUM(S2:S45)</f>
+        <v/>
+      </c>
+      <c r="T46" s="102">
+        <f>SUM(T2:T45)</f>
+        <v/>
+      </c>
+      <c r="U46" s="102">
+        <f>SUM(U2:U45)</f>
+        <v/>
+      </c>
+      <c r="V46" s="102">
+        <f>SUM(V2:V45)</f>
+        <v/>
+      </c>
+      <c r="W46" s="102">
+        <f>SUM(W2:W45)</f>
         <v/>
       </c>
     </row>
@@ -4630,7 +4754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="13.25" customWidth="1" style="97" min="1" max="1"/>
@@ -4760,7 +4884,7 @@
       </c>
       <c r="F3" s="120" t="n"/>
       <c r="G3" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A3)</f>
+        <f>SUMIFS(입금현황!$46:$46,입금현황!$1:$1,원장!$A3)</f>
         <v/>
       </c>
       <c r="H3" s="121">
@@ -4869,7 +4993,7 @@
       </c>
       <c r="F6" s="120" t="n"/>
       <c r="G6" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A6)</f>
+        <f>SUMIFS(입금현황!$46:$46,입금현황!$1:$1,원장!$A6)</f>
         <v/>
       </c>
       <c r="H6" s="121">
@@ -5086,7 +5210,7 @@
       </c>
       <c r="F12" s="137" t="n"/>
       <c r="G12" s="137">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A12)</f>
+        <f>SUMIFS(입금현황!$46:$46,입금현황!$1:$1,원장!$A12)</f>
         <v/>
       </c>
       <c r="H12" s="138">
@@ -5123,7 +5247,7 @@
       </c>
       <c r="F13" s="120" t="n"/>
       <c r="G13" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A13)</f>
+        <f>SUMIFS(입금현황!$46:$46,입금현황!$1:$1,원장!$A13)</f>
         <v/>
       </c>
       <c r="H13" s="121">
@@ -5160,7 +5284,7 @@
       </c>
       <c r="F14" s="120" t="n"/>
       <c r="G14" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A14)</f>
+        <f>SUMIFS(입금현황!$46:$46,입금현황!$1:$1,원장!$A14)</f>
         <v/>
       </c>
       <c r="H14" s="121">
@@ -5197,7 +5321,7 @@
       </c>
       <c r="F15" s="120" t="n"/>
       <c r="G15" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A15)</f>
+        <f>SUMIFS(입금현황!$46:$46,입금현황!$1:$1,원장!$A15)</f>
         <v/>
       </c>
       <c r="H15" s="121">
@@ -5234,7 +5358,7 @@
       </c>
       <c r="F16" s="120" t="n"/>
       <c r="G16" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A16)</f>
+        <f>SUMIFS(입금현황!$46:$46,입금현황!$1:$1,원장!$A16)</f>
         <v/>
       </c>
       <c r="H16" s="121">
@@ -5271,7 +5395,7 @@
       </c>
       <c r="F17" s="120" t="n"/>
       <c r="G17" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A17)</f>
+        <f>SUMIFS(입금현황!$46:$46,입금현황!$1:$1,원장!$A17)</f>
         <v/>
       </c>
       <c r="H17" s="121">
@@ -5380,7 +5504,7 @@
       </c>
       <c r="F20" s="137" t="n"/>
       <c r="G20" s="137">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A20)</f>
+        <f>SUMIFS(입금현황!$46:$46,입금현황!$1:$1,원장!$A20)</f>
         <v/>
       </c>
       <c r="H20" s="138">
@@ -5439,6 +5563,78 @@
       <c r="G22" s="137" t="n"/>
       <c r="H22" s="138" t="n"/>
       <c r="I22" s="139" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4">
+        <f>RIGHT(YEAR(C23),2)&amp;"년 "&amp;MONTH(C23)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B23" s="4">
+        <f>VLOOKUP(WEEKDAY(C23,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C23" s="136" t="n">
+        <v>46277</v>
+      </c>
+      <c r="D23" s="136" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="E23" s="136" t="inlineStr">
+        <is>
+          <t>모임비</t>
+        </is>
+      </c>
+      <c r="F23" s="137" t="n">
+        <v>262000</v>
+      </c>
+      <c r="G23" s="137" t="n"/>
+      <c r="H23" s="138">
+        <f>G23-F23</f>
+        <v/>
+      </c>
+      <c r="I23" s="139" t="inlineStr">
+        <is>
+          <t>점심식대</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4">
+        <f>RIGHT(YEAR(C24),2)&amp;"년 "&amp;MONTH(C24)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B24" s="4">
+        <f>VLOOKUP(WEEKDAY(C24,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C24" s="136" t="n">
+        <v>46291</v>
+      </c>
+      <c r="D24" s="136" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="E24" s="136" t="inlineStr">
+        <is>
+          <t>이자</t>
+        </is>
+      </c>
+      <c r="F24" s="137" t="n"/>
+      <c r="G24" s="137" t="n">
+        <v>129</v>
+      </c>
+      <c r="H24" s="138">
+        <f>G24-F24</f>
+        <v/>
+      </c>
+      <c r="I24" s="139" t="inlineStr">
+        <is>
+          <t>입출금통장 이자</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
